--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -1,31 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A5/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6667" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07FB3E30-453A-4946-9676-970FEF94237C}"/>
+  <xr:revisionPtr revIDLastSave="6725" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D793AC53-AD66-43B7-9553-E8BADDAF7A53}"/>
   <bookViews>
-    <workbookView xWindow="5364" yWindow="2172" windowWidth="14892" windowHeight="10404" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="0" windowWidth="18228" windowHeight="12336" tabRatio="445" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="SEP25" sheetId="89" r:id="rId1"/>
-    <sheet name="SEP24" sheetId="77" r:id="rId2"/>
-    <sheet name="AUG25" sheetId="88" r:id="rId3"/>
-    <sheet name="JUL25" sheetId="87" r:id="rId4"/>
-    <sheet name="JUN25" sheetId="86" r:id="rId5"/>
-    <sheet name="MAY25" sheetId="85" r:id="rId6"/>
-    <sheet name="APR25" sheetId="84" r:id="rId7"/>
-    <sheet name="MAR25" sheetId="83" r:id="rId8"/>
-    <sheet name="FEB25" sheetId="82" r:id="rId9"/>
-    <sheet name="JAN25" sheetId="81" r:id="rId10"/>
-    <sheet name="DEC24" sheetId="80" r:id="rId11"/>
-    <sheet name="NOV24" sheetId="79" r:id="rId12"/>
-    <sheet name="OCT24" sheetId="78" r:id="rId13"/>
+    <sheet name="NOV25" sheetId="91" r:id="rId1"/>
+    <sheet name="OCT25" sheetId="90" r:id="rId2"/>
+    <sheet name="SEP25" sheetId="89" r:id="rId3"/>
+    <sheet name="AUG25" sheetId="88" r:id="rId4"/>
+    <sheet name="JUL25" sheetId="87" r:id="rId5"/>
+    <sheet name="JUN25" sheetId="86" r:id="rId6"/>
+    <sheet name="MAY25" sheetId="85" r:id="rId7"/>
+    <sheet name="APR25" sheetId="84" r:id="rId8"/>
+    <sheet name="MAR25" sheetId="83" r:id="rId9"/>
+    <sheet name="FEB25" sheetId="82" r:id="rId10"/>
+    <sheet name="JAN25" sheetId="81" r:id="rId11"/>
+    <sheet name="DEC24" sheetId="80" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -48,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="66">
   <si>
     <t>Name</t>
   </si>
@@ -456,7 +455,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -533,7 +532,6 @@
     <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -612,10 +610,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -965,6 +959,2338 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F537F07A-D0A7-416B-8994-ABDD1C22435D}">
+  <dimension ref="A1:N18"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A2" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="28">
+        <v>44846</v>
+      </c>
+      <c r="C2" s="29">
+        <v>0</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="31"/>
+      <c r="F2" s="37">
+        <v>1.3</v>
+      </c>
+      <c r="G2" s="31">
+        <f>C2*F2</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="32">
+        <f>G2*0.9</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="34">
+        <f>SUM(H2:H2)</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="28">
+        <v>45590</v>
+      </c>
+      <c r="C4" s="29">
+        <v>1500</v>
+      </c>
+      <c r="D4" s="30">
+        <v>12</v>
+      </c>
+      <c r="E4" s="31">
+        <v>19756.14</v>
+      </c>
+      <c r="F4" s="30">
+        <v>0</v>
+      </c>
+      <c r="G4" s="31">
+        <v>19756.14</v>
+      </c>
+      <c r="H4" s="40">
+        <f>G4-E4</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="26"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="32">
+        <f>SUM(E4:E4)</f>
+        <v>19756.14</v>
+      </c>
+      <c r="F5" s="30"/>
+      <c r="G5" s="32">
+        <f>SUM(G4:G4)</f>
+        <v>19756.14</v>
+      </c>
+      <c r="H5" s="32">
+        <f>SUM(H4:H4)</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="7"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="26"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="43">
+        <f>H3+H5</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="7">
+        <v>30614.600000000002</v>
+      </c>
+      <c r="K6" s="7"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="26"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="32">
+        <v>-522636.73</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="7">
+        <v>-553251.32999999996</v>
+      </c>
+      <c r="K7" s="7"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+    </row>
+    <row r="8" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="26"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="41">
+        <f>H6+H7</f>
+        <v>-522636.73</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8" s="7">
+        <v>-522636.73</v>
+      </c>
+      <c r="K8" s="7"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+    </row>
+    <row r="9" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="26"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="35">
+        <v>396550</v>
+      </c>
+      <c r="I9" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="7">
+        <v>386420</v>
+      </c>
+      <c r="K9" s="7"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+    </row>
+    <row r="10" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="26"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="35">
+        <v>24420</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" s="7">
+        <v>10130</v>
+      </c>
+      <c r="K10" s="7"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A11" s="26"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="41">
+        <f>H9+H10</f>
+        <v>420970</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="7">
+        <v>396550</v>
+      </c>
+      <c r="K11" s="7"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A12" s="5"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="45">
+        <f>H8-H11</f>
+        <v>-943606.73</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="7">
+        <v>-919186.73</v>
+      </c>
+      <c r="K12" s="7"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="5"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="7">
+        <v>57000</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" s="7">
+        <v>57000</v>
+      </c>
+      <c r="K13" s="7"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A14" s="6"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="42">
+        <f>H12+H13</f>
+        <v>-886606.73</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="J14" s="7">
+        <v>-862186.73</v>
+      </c>
+      <c r="K14" s="7"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K15" s="7"/>
+      <c r="M15" s="7"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M16" s="7"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M17" s="7"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C18" s="12"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="10"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="7"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F818BAB4-5237-4BD8-9A61-131DACEE1BB2}">
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.75" style="12" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="10.25" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.125" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="19.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.25" style="11" customWidth="1"/>
+    <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
+    <col min="11" max="11" width="13" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="10.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="5"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A2" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="28">
+        <v>45705</v>
+      </c>
+      <c r="C2" s="29">
+        <v>4500</v>
+      </c>
+      <c r="D2" s="61">
+        <v>31</v>
+      </c>
+      <c r="E2" s="61">
+        <v>139808.98000000001</v>
+      </c>
+      <c r="F2" s="30">
+        <v>7.35</v>
+      </c>
+      <c r="G2" s="64">
+        <v>33001.74</v>
+      </c>
+      <c r="H2" s="65">
+        <f>G2-E2</f>
+        <v>-106807.24000000002</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="28">
+        <v>45705</v>
+      </c>
+      <c r="C3" s="29">
+        <v>1500</v>
+      </c>
+      <c r="D3" s="61">
+        <v>12</v>
+      </c>
+      <c r="E3" s="61">
+        <v>18039.87</v>
+      </c>
+      <c r="F3" s="30">
+        <v>7.35</v>
+      </c>
+      <c r="G3" s="64">
+        <v>11000.58</v>
+      </c>
+      <c r="H3" s="65">
+        <f>G3-E3</f>
+        <v>-7039.2899999999991</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="28">
+        <v>45712</v>
+      </c>
+      <c r="C4" s="29">
+        <v>15000</v>
+      </c>
+      <c r="D4" s="62">
+        <v>10.9</v>
+      </c>
+      <c r="E4" s="61">
+        <v>163862.14000000001</v>
+      </c>
+      <c r="F4" s="30">
+        <v>2.94</v>
+      </c>
+      <c r="G4" s="66">
+        <v>44002.32</v>
+      </c>
+      <c r="H4" s="65">
+        <f>G4-E4</f>
+        <v>-119859.82</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A5" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="28">
+        <v>45712</v>
+      </c>
+      <c r="C5" s="29">
+        <v>12000</v>
+      </c>
+      <c r="D5" s="62">
+        <v>10</v>
+      </c>
+      <c r="E5" s="61">
+        <v>120265.79</v>
+      </c>
+      <c r="F5" s="30">
+        <v>2.94</v>
+      </c>
+      <c r="G5" s="66">
+        <v>35201.86</v>
+      </c>
+      <c r="H5" s="65">
+        <f>G5-E5</f>
+        <v>-85063.93</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="28">
+        <v>45712</v>
+      </c>
+      <c r="C6" s="29">
+        <v>9000</v>
+      </c>
+      <c r="D6" s="62">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="E6" s="61">
+        <v>83885.39</v>
+      </c>
+      <c r="F6" s="30">
+        <v>2.94</v>
+      </c>
+      <c r="G6" s="66">
+        <v>26401.4</v>
+      </c>
+      <c r="H6" s="65">
+        <f>G6-E6</f>
+        <v>-57483.99</v>
+      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A7" s="27"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="65">
+        <f>SUM(H2:H6)</f>
+        <v>-376254.27</v>
+      </c>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="26"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="65">
+        <f>H7</f>
+        <v>-376254.27</v>
+      </c>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="L8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="26"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="65" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="65">
+        <v>321444.99525200005</v>
+      </c>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="L9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="26"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="65" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="67">
+        <f>SUM(H8,H9)</f>
+        <v>-54809.274747999967</v>
+      </c>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="L10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="26"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="68">
+        <v>43930</v>
+      </c>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="L11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="26"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="68">
+        <v>58500</v>
+      </c>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="L12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="26"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="60" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" s="65" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="67">
+        <f>H11+H12</f>
+        <v>102430</v>
+      </c>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="L13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="26"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="69">
+        <f>H10-H13</f>
+        <v>-157239.27474799997</v>
+      </c>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="L14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="26"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="60" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15" s="65" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="65">
+        <v>57000</v>
+      </c>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="L15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="26"/>
+      <c r="B16" s="63"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="70">
+        <f>H14+H15</f>
+        <v>-100239.27474799997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="26"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="65"/>
+      <c r="H17" s="65"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="26"/>
+      <c r="B18" s="63"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="60" t="s">
+        <v>62</v>
+      </c>
+      <c r="G18" s="71" t="s">
+        <v>63</v>
+      </c>
+      <c r="H18" s="65">
+        <f>H15-H13</f>
+        <v>-45430</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32283096-5907-4E30-9E76-682BE04B55EC}">
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.25" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="8" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16" style="7" customWidth="1"/>
+    <col min="8" max="8" width="13.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.375" style="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.875" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="8.625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="5"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A2" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="28">
+        <v>45288</v>
+      </c>
+      <c r="C2" s="29">
+        <v>22500</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="31"/>
+      <c r="F2" s="37">
+        <v>0</v>
+      </c>
+      <c r="G2" s="31">
+        <f t="shared" ref="G2" si="0">C2*F2</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="32">
+        <f>G2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="32">
+        <f>SUM(H2,H2)</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="28">
+        <v>45295</v>
+      </c>
+      <c r="C4" s="29">
+        <v>2000</v>
+      </c>
+      <c r="D4" s="30">
+        <v>21.7</v>
+      </c>
+      <c r="E4" s="31">
+        <v>43496.13</v>
+      </c>
+      <c r="F4" s="30">
+        <v>22.9</v>
+      </c>
+      <c r="G4" s="31">
+        <v>45698.55</v>
+      </c>
+      <c r="H4" s="32">
+        <v>0</v>
+      </c>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="26"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="32">
+        <f>SUM(E4:E4)</f>
+        <v>43496.13</v>
+      </c>
+      <c r="F5" s="30"/>
+      <c r="G5" s="32">
+        <f>SUM(G4:G4)</f>
+        <v>45698.55</v>
+      </c>
+      <c r="H5" s="32">
+        <f>SUM(H4:H4)</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="15"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="26"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="34">
+        <f>H3+H5</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="26"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="32">
+        <v>308374.99525200005</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+    </row>
+    <row r="8" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="26"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="41">
+        <f>H6+H7</f>
+        <v>308374.99525200005</v>
+      </c>
+      <c r="I8" s="11"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+    </row>
+    <row r="9" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="26"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="35">
+        <v>0</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+    </row>
+    <row r="10" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="26"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="35">
+        <v>43930</v>
+      </c>
+      <c r="I10" s="11"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A11" s="26"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="41">
+        <f>H9+H10</f>
+        <v>43930</v>
+      </c>
+      <c r="I11" s="11"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A12" s="5"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="36">
+        <f>H8-H11</f>
+        <v>264444.99525200005</v>
+      </c>
+      <c r="I12" s="11"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="5"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="38">
+        <v>57000</v>
+      </c>
+      <c r="I13" s="11"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A14" s="6"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="48">
+        <f>H12+H13</f>
+        <v>321444.99525200005</v>
+      </c>
+      <c r="I14" s="11"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="6"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70859943-B961-4C68-A873-2ACB6A8732BB}">
+  <dimension ref="A1:N28"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="14.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
+    <col min="11" max="11" width="13" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A2" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="28">
+        <v>45632</v>
+      </c>
+      <c r="C2" s="29">
+        <v>35000</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="31"/>
+      <c r="F2" s="37">
+        <v>0.22220000000000001</v>
+      </c>
+      <c r="G2" s="31">
+        <f t="shared" ref="G2:G12" si="0">C2*F2</f>
+        <v>7777</v>
+      </c>
+      <c r="H2" s="40">
+        <f t="shared" ref="H2:H11" si="1">G2*0.9</f>
+        <v>6999.3</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A3" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="28">
+        <v>45632</v>
+      </c>
+      <c r="C3" s="29">
+        <v>27000</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="31"/>
+      <c r="F3" s="37">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="31">
+        <f t="shared" si="0"/>
+        <v>13500</v>
+      </c>
+      <c r="H3" s="40">
+        <f t="shared" si="1"/>
+        <v>12150</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A4" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="28">
+        <v>45637</v>
+      </c>
+      <c r="C4" s="29">
+        <v>7200</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="31"/>
+      <c r="F4" s="37">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="G4" s="31">
+        <f t="shared" si="0"/>
+        <v>1260</v>
+      </c>
+      <c r="H4" s="40">
+        <f t="shared" si="1"/>
+        <v>1134</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A5" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="28">
+        <v>45638</v>
+      </c>
+      <c r="C5" s="29">
+        <v>55000</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="31"/>
+      <c r="F5" s="37">
+        <v>0.2213</v>
+      </c>
+      <c r="G5" s="31">
+        <f t="shared" si="0"/>
+        <v>12171.5</v>
+      </c>
+      <c r="H5" s="40">
+        <f t="shared" si="1"/>
+        <v>10954.35</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A6" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="28">
+        <v>45638</v>
+      </c>
+      <c r="C6" s="29">
+        <v>3600</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="31"/>
+      <c r="F6" s="37">
+        <v>0.1</v>
+      </c>
+      <c r="G6" s="31">
+        <f t="shared" si="0"/>
+        <v>360</v>
+      </c>
+      <c r="H6" s="40">
+        <f t="shared" si="1"/>
+        <v>324</v>
+      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A7" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="28">
+        <v>45639</v>
+      </c>
+      <c r="C7" s="29">
+        <v>12500</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="31"/>
+      <c r="F7" s="37">
+        <v>0.215</v>
+      </c>
+      <c r="G7" s="31">
+        <f t="shared" si="0"/>
+        <v>2687.5</v>
+      </c>
+      <c r="H7" s="40">
+        <f t="shared" si="1"/>
+        <v>2418.75</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A8" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="28">
+        <v>45639</v>
+      </c>
+      <c r="C8" s="29">
+        <v>50000</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="31"/>
+      <c r="F8" s="37">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="G8" s="31">
+        <f t="shared" si="0"/>
+        <v>1050</v>
+      </c>
+      <c r="H8" s="40">
+        <f t="shared" si="1"/>
+        <v>945</v>
+      </c>
+      <c r="I8" s="11"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A9" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="28">
+        <v>45639</v>
+      </c>
+      <c r="C9" s="29">
+        <v>20000</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="31"/>
+      <c r="F9" s="37">
+        <v>0.193</v>
+      </c>
+      <c r="G9" s="31">
+        <f t="shared" si="0"/>
+        <v>3860</v>
+      </c>
+      <c r="H9" s="40">
+        <f t="shared" si="1"/>
+        <v>3474</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A10" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="28">
+        <v>45643</v>
+      </c>
+      <c r="C10" s="29">
+        <v>50000</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="31"/>
+      <c r="F10" s="37">
+        <v>0.22289999999999999</v>
+      </c>
+      <c r="G10" s="31">
+        <f t="shared" si="0"/>
+        <v>11145</v>
+      </c>
+      <c r="H10" s="40">
+        <f t="shared" si="1"/>
+        <v>10030.5</v>
+      </c>
+      <c r="I10" s="11"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A11" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="28">
+        <v>45651</v>
+      </c>
+      <c r="C11" s="29">
+        <v>60000</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="31"/>
+      <c r="F11" s="37">
+        <v>0.19980000000000001</v>
+      </c>
+      <c r="G11" s="31">
+        <f t="shared" si="0"/>
+        <v>11988</v>
+      </c>
+      <c r="H11" s="40">
+        <f t="shared" si="1"/>
+        <v>10789.2</v>
+      </c>
+      <c r="I11" s="11"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A12" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="28">
+        <v>45653</v>
+      </c>
+      <c r="C12" s="29">
+        <v>20000</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="31"/>
+      <c r="F12" s="37">
+        <v>0.1192</v>
+      </c>
+      <c r="G12" s="31">
+        <f t="shared" si="0"/>
+        <v>2384</v>
+      </c>
+      <c r="H12" s="40">
+        <f>G12</f>
+        <v>2384</v>
+      </c>
+      <c r="I12" s="11"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="27"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="34">
+        <f>SUM(H2:H12)</f>
+        <v>61603.100000000006</v>
+      </c>
+      <c r="I13" s="11"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A14" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="28">
+        <v>37617</v>
+      </c>
+      <c r="C14" s="29">
+        <v>0</v>
+      </c>
+      <c r="D14" s="30">
+        <v>21.3</v>
+      </c>
+      <c r="E14" s="31">
+        <v>0</v>
+      </c>
+      <c r="F14" s="30">
+        <v>21.3</v>
+      </c>
+      <c r="G14" s="31">
+        <v>0</v>
+      </c>
+      <c r="H14" s="32">
+        <f t="shared" ref="H14" si="2">G14-E14</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="11"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="26"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="32">
+        <f>SUM(E14:E14)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="30"/>
+      <c r="G15" s="32">
+        <f>SUM(G14:G14)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="40">
+        <f>SUM(H14:H14)</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="7"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+    </row>
+    <row r="16" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A16" s="26"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="34">
+        <f>H13+H15</f>
+        <v>61603.100000000006</v>
+      </c>
+      <c r="I16" s="11"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="26"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="32">
+        <v>318141.89525200002</v>
+      </c>
+      <c r="K17" s="7"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+    </row>
+    <row r="18" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="26"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18" s="41">
+        <f>H16+H17</f>
+        <v>379744.99525200005</v>
+      </c>
+      <c r="K18" s="7"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+    </row>
+    <row r="19" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="26"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="35">
+        <v>701370</v>
+      </c>
+      <c r="K19" s="7"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+    </row>
+    <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="26"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="H20" s="35">
+        <v>38000</v>
+      </c>
+      <c r="K20" s="7"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+    </row>
+    <row r="21" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A21" s="26"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="41">
+        <f>H19+H20</f>
+        <v>739370</v>
+      </c>
+      <c r="I21" s="11"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="6"/>
+    </row>
+    <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A22" s="5"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="36">
+        <f>H18-H21</f>
+        <v>-359625.00474799995</v>
+      </c>
+      <c r="I22" s="11"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="6"/>
+    </row>
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A23" s="5"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" s="38">
+        <v>668000</v>
+      </c>
+      <c r="I23" s="11"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="6"/>
+    </row>
+    <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A24" s="6"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="H24" s="48">
+        <f>H22+H23</f>
+        <v>308374.99525200005</v>
+      </c>
+      <c r="I24" s="11"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="6"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K25" s="7"/>
+      <c r="M25" s="7"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M26" s="7"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M27" s="7"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C28" s="12"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="10"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="7"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I12">
+    <sortCondition ref="B2:B12"/>
+    <sortCondition ref="A2:A12"/>
+  </sortState>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801544F9-630F-4E32-B67B-5CF42760770C}">
+  <dimension ref="A1:N20"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.25" style="11" customWidth="1"/>
+    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A2" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="28">
+        <v>45576</v>
+      </c>
+      <c r="C2" s="29">
+        <v>6800</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="31"/>
+      <c r="F2" s="55">
+        <v>0</v>
+      </c>
+      <c r="G2" s="31">
+        <f>C2*F2</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="56">
+        <f>G2*0.9</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="34">
+        <f>SUM(H2:H2)</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="28">
+        <v>45931</v>
+      </c>
+      <c r="C4" s="29">
+        <v>10000</v>
+      </c>
+      <c r="D4" s="30">
+        <v>2.62</v>
+      </c>
+      <c r="E4" s="31">
+        <v>26258.03</v>
+      </c>
+      <c r="F4" s="30">
+        <v>2.72</v>
+      </c>
+      <c r="G4" s="31">
+        <v>27139.759999999998</v>
+      </c>
+      <c r="H4" s="40">
+        <f>G4-E4</f>
+        <v>881.72999999999956</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A5" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="28">
+        <v>45937</v>
+      </c>
+      <c r="C5" s="29">
+        <v>3000</v>
+      </c>
+      <c r="D5" s="30">
+        <v>26</v>
+      </c>
+      <c r="E5" s="31">
+        <v>78172.759999999995</v>
+      </c>
+      <c r="F5" s="30">
+        <v>26.5</v>
+      </c>
+      <c r="G5" s="31">
+        <v>79323.91</v>
+      </c>
+      <c r="H5" s="40">
+        <f>G5-E5</f>
+        <v>1151.1500000000087</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="28">
+        <v>45954</v>
+      </c>
+      <c r="C6" s="29">
+        <v>2500</v>
+      </c>
+      <c r="D6" s="30">
+        <v>31</v>
+      </c>
+      <c r="E6" s="31">
+        <v>77671.66</v>
+      </c>
+      <c r="F6" s="30">
+        <v>31.25</v>
+      </c>
+      <c r="G6" s="31">
+        <v>77951.960000000006</v>
+      </c>
+      <c r="H6" s="40">
+        <f>G6-E6</f>
+        <v>280.30000000000291</v>
+      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="26"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="32">
+        <f>SUM(E4:E6)</f>
+        <v>182102.45</v>
+      </c>
+      <c r="F7" s="30"/>
+      <c r="G7" s="32">
+        <f t="shared" ref="G7:H7" si="0">SUM(G4:G6)</f>
+        <v>184415.63</v>
+      </c>
+      <c r="H7" s="32">
+        <f t="shared" si="0"/>
+        <v>2313.1800000000112</v>
+      </c>
+      <c r="K7" s="7"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A8" s="26"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="34">
+        <f>H3+H7</f>
+        <v>2313.1800000000112</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="7">
+        <v>30614.600000000002</v>
+      </c>
+      <c r="K8" s="7"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="26"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="32">
+        <v>-522636.73</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="7">
+        <v>-553251.32999999996</v>
+      </c>
+      <c r="K9" s="7"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+    </row>
+    <row r="10" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="26"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="41">
+        <f>H8+H9</f>
+        <v>-520323.55</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10" s="7">
+        <v>-522636.73</v>
+      </c>
+      <c r="K10" s="7"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+    </row>
+    <row r="11" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="26"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="35">
+        <v>396550</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="7">
+        <v>386420</v>
+      </c>
+      <c r="K11" s="7"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+    </row>
+    <row r="12" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="26"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12" s="35">
+        <v>19270</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="J12" s="7">
+        <v>10130</v>
+      </c>
+      <c r="K12" s="7"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="26"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="41">
+        <f>H11+H12</f>
+        <v>415820</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="7">
+        <v>396550</v>
+      </c>
+      <c r="K13" s="7"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A14" s="5"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="45">
+        <f>H10-H13</f>
+        <v>-936143.55</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="7">
+        <v>-919186.73</v>
+      </c>
+      <c r="K14" s="7"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A15" s="5"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="38">
+        <v>57000</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" s="7">
+        <v>57000</v>
+      </c>
+      <c r="K15" s="7"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A16" s="6"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="42">
+        <f>H14+H15</f>
+        <v>-879143.55</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="J16" s="7">
+        <v>-862186.73</v>
+      </c>
+      <c r="K16" s="7"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="K17" s="7"/>
+      <c r="M17" s="7"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M18" s="7"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M19" s="7"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C20" s="12"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="10"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="7"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{805BC19F-42DC-4CD3-B954-E9F19E56BFF7}">
   <dimension ref="A1:N40"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -1011,7 +3337,7 @@
       <c r="H1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="59"/>
+      <c r="I1" s="58"/>
       <c r="J1" s="5"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
@@ -1019,24 +3345,24 @@
       <c r="N1" s="6"/>
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="83" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="85">
+      <c r="B2" s="84">
         <v>45903</v>
       </c>
-      <c r="C2" s="86">
+      <c r="C2" s="85">
         <v>120000</v>
       </c>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84">
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83">
         <v>0.15454999999999999</v>
       </c>
-      <c r="G2" s="89">
+      <c r="G2" s="88">
         <v>18546</v>
       </c>
-      <c r="H2" s="89">
+      <c r="H2" s="88">
         <v>16691.400000000001</v>
       </c>
       <c r="I2" s="10"/>
@@ -1047,24 +3373,24 @@
       <c r="N2" s="6"/>
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="83" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="85">
+      <c r="B3" s="84">
         <v>45910</v>
       </c>
-      <c r="C3" s="86">
+      <c r="C3" s="85">
         <v>1200</v>
       </c>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="90">
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="89">
         <v>0.31</v>
       </c>
-      <c r="G3" s="89">
+      <c r="G3" s="88">
         <v>372</v>
       </c>
-      <c r="H3" s="89">
+      <c r="H3" s="88">
         <v>339.6</v>
       </c>
       <c r="I3" s="10"/>
@@ -1075,24 +3401,24 @@
       <c r="N3" s="6"/>
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A4" s="84" t="s">
+      <c r="A4" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="85">
+      <c r="B4" s="84">
         <v>45905</v>
       </c>
-      <c r="C4" s="91">
+      <c r="C4" s="90">
         <v>17500</v>
       </c>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="90">
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="89">
         <v>0.20499999999999999</v>
       </c>
-      <c r="G4" s="89">
+      <c r="G4" s="88">
         <v>3587.5</v>
       </c>
-      <c r="H4" s="89">
+      <c r="H4" s="88">
         <v>3228.75</v>
       </c>
       <c r="I4" s="10"/>
@@ -1103,24 +3429,24 @@
       <c r="N4" s="6"/>
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A5" s="84" t="s">
+      <c r="A5" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="85">
+      <c r="B5" s="84">
         <v>45912</v>
       </c>
-      <c r="C5" s="86">
+      <c r="C5" s="85">
         <v>4000</v>
       </c>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="90">
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="89">
         <v>0.15</v>
       </c>
-      <c r="G5" s="89">
+      <c r="G5" s="88">
         <v>600</v>
       </c>
-      <c r="H5" s="89">
+      <c r="H5" s="88">
         <v>540</v>
       </c>
       <c r="I5" s="10"/>
@@ -1131,24 +3457,24 @@
       <c r="N5" s="6"/>
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A6" s="84" t="s">
+      <c r="A6" s="83" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="85">
+      <c r="B6" s="84">
         <v>45912</v>
       </c>
-      <c r="C6" s="86">
+      <c r="C6" s="85">
         <v>5000</v>
       </c>
-      <c r="D6" s="84"/>
-      <c r="E6" s="84"/>
-      <c r="F6" s="84">
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83">
         <v>1</v>
       </c>
-      <c r="G6" s="89">
+      <c r="G6" s="88">
         <v>5000</v>
       </c>
-      <c r="H6" s="89">
+      <c r="H6" s="88">
         <v>4500</v>
       </c>
       <c r="I6" s="10"/>
@@ -1159,24 +3485,24 @@
       <c r="N6" s="6"/>
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="84" t="s">
+      <c r="A7" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="85">
+      <c r="B7" s="84">
         <v>45911</v>
       </c>
-      <c r="C7" s="92">
+      <c r="C7" s="91">
         <v>55000</v>
       </c>
-      <c r="D7" s="84"/>
-      <c r="E7" s="84"/>
-      <c r="F7" s="90">
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="89">
         <v>0.2261</v>
       </c>
-      <c r="G7" s="89">
+      <c r="G7" s="88">
         <v>12435.5</v>
       </c>
-      <c r="H7" s="89">
+      <c r="H7" s="88">
         <v>11191.95</v>
       </c>
       <c r="I7" s="10"/>
@@ -1187,24 +3513,24 @@
       <c r="N7" s="6"/>
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="84" t="s">
+      <c r="A8" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="85">
+      <c r="B8" s="84">
         <v>45909</v>
       </c>
-      <c r="C8" s="91">
+      <c r="C8" s="90">
         <v>50000</v>
       </c>
-      <c r="D8" s="84"/>
-      <c r="E8" s="84"/>
-      <c r="F8" s="84">
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83">
         <v>0.22220000000000001</v>
       </c>
-      <c r="G8" s="89">
+      <c r="G8" s="88">
         <v>11110</v>
       </c>
-      <c r="H8" s="89">
+      <c r="H8" s="88">
         <v>9999</v>
       </c>
       <c r="I8" s="10"/>
@@ -1215,24 +3541,24 @@
       <c r="N8" s="6"/>
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A9" s="84" t="s">
+      <c r="A9" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="85">
+      <c r="B9" s="84">
         <v>45911</v>
       </c>
-      <c r="C9" s="91">
+      <c r="C9" s="90">
         <v>69000</v>
       </c>
-      <c r="D9" s="84"/>
-      <c r="E9" s="84"/>
-      <c r="F9" s="90">
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="89">
         <v>0.19650000000000001</v>
       </c>
-      <c r="G9" s="89">
+      <c r="G9" s="88">
         <v>13558.5</v>
       </c>
-      <c r="H9" s="89">
+      <c r="H9" s="88">
         <v>12202.65</v>
       </c>
       <c r="I9" s="10"/>
@@ -1243,24 +3569,24 @@
       <c r="N9" s="6"/>
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="84" t="s">
+      <c r="A10" s="83" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="85">
+      <c r="B10" s="84">
         <v>45911</v>
       </c>
-      <c r="C10" s="92">
+      <c r="C10" s="91">
         <v>7200</v>
       </c>
-      <c r="D10" s="84"/>
-      <c r="E10" s="84"/>
-      <c r="F10" s="84">
+      <c r="D10" s="83"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83">
         <v>0.17499999999999999</v>
       </c>
-      <c r="G10" s="89">
+      <c r="G10" s="88">
         <v>1260</v>
       </c>
-      <c r="H10" s="89">
+      <c r="H10" s="88">
         <v>1134</v>
       </c>
       <c r="I10" s="10"/>
@@ -1271,24 +3597,24 @@
       <c r="N10" s="6"/>
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A11" s="84" t="s">
+      <c r="A11" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="85">
+      <c r="B11" s="84">
         <v>45912</v>
       </c>
-      <c r="C11" s="92">
+      <c r="C11" s="91">
         <v>4200</v>
       </c>
-      <c r="D11" s="84"/>
-      <c r="E11" s="84"/>
-      <c r="F11" s="93">
+      <c r="D11" s="83"/>
+      <c r="E11" s="83"/>
+      <c r="F11" s="92">
         <v>0.24</v>
       </c>
-      <c r="G11" s="89">
+      <c r="G11" s="88">
         <v>1008</v>
       </c>
-      <c r="H11" s="89">
+      <c r="H11" s="88">
         <v>907.2</v>
       </c>
       <c r="I11" s="10"/>
@@ -1299,24 +3625,24 @@
       <c r="N11" s="6"/>
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="84" t="s">
+      <c r="A12" s="83" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="85">
+      <c r="B12" s="84">
         <v>45910</v>
       </c>
-      <c r="C12" s="91">
+      <c r="C12" s="90">
         <v>81000</v>
       </c>
-      <c r="D12" s="84"/>
-      <c r="E12" s="84"/>
-      <c r="F12" s="90">
+      <c r="D12" s="83"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="89">
         <v>0.25</v>
       </c>
-      <c r="G12" s="89">
+      <c r="G12" s="88">
         <v>20250</v>
       </c>
-      <c r="H12" s="89">
+      <c r="H12" s="88">
         <v>19926</v>
       </c>
       <c r="I12" s="10"/>
@@ -1327,24 +3653,24 @@
       <c r="N12" s="6"/>
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="84" t="s">
+      <c r="A13" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="85">
+      <c r="B13" s="84">
         <v>45905</v>
       </c>
-      <c r="C13" s="86">
+      <c r="C13" s="85">
         <v>27000</v>
       </c>
-      <c r="D13" s="84"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="84">
+      <c r="D13" s="83"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83">
         <v>0.05</v>
       </c>
-      <c r="G13" s="89">
+      <c r="G13" s="88">
         <v>1350</v>
       </c>
-      <c r="H13" s="89">
+      <c r="H13" s="88">
         <v>1350</v>
       </c>
       <c r="I13" s="10"/>
@@ -1355,24 +3681,24 @@
       <c r="N13" s="6"/>
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A14" s="84" t="s">
+      <c r="A14" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="85">
+      <c r="B14" s="84">
         <v>45905</v>
       </c>
-      <c r="C14" s="86">
+      <c r="C14" s="85">
         <v>27000</v>
       </c>
-      <c r="D14" s="84"/>
-      <c r="E14" s="84"/>
-      <c r="F14" s="84">
+      <c r="D14" s="83"/>
+      <c r="E14" s="83"/>
+      <c r="F14" s="83">
         <v>0.5</v>
       </c>
-      <c r="G14" s="89">
+      <c r="G14" s="88">
         <v>13500</v>
       </c>
-      <c r="H14" s="89">
+      <c r="H14" s="88">
         <v>12825</v>
       </c>
       <c r="I14" s="10"/>
@@ -1383,24 +3709,24 @@
       <c r="N14" s="6"/>
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A15" s="84" t="s">
+      <c r="A15" s="83" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="85">
+      <c r="B15" s="84">
         <v>45910</v>
       </c>
-      <c r="C15" s="91">
+      <c r="C15" s="90">
         <v>17500</v>
       </c>
-      <c r="D15" s="84"/>
-      <c r="E15" s="84"/>
-      <c r="F15" s="84">
+      <c r="D15" s="83"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="83">
         <v>0.1</v>
       </c>
-      <c r="G15" s="89">
+      <c r="G15" s="88">
         <v>1750</v>
       </c>
-      <c r="H15" s="89">
+      <c r="H15" s="88">
         <v>1575</v>
       </c>
       <c r="I15" s="10"/>
@@ -1411,24 +3737,24 @@
       <c r="N15" s="6"/>
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A16" s="84" t="s">
+      <c r="A16" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="85">
+      <c r="B16" s="84">
         <v>45915</v>
       </c>
-      <c r="C16" s="86">
+      <c r="C16" s="85">
         <v>20000</v>
       </c>
-      <c r="D16" s="84"/>
-      <c r="E16" s="84"/>
-      <c r="F16" s="90">
+      <c r="D16" s="83"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="89">
         <v>0.1128</v>
       </c>
-      <c r="G16" s="89">
+      <c r="G16" s="88">
         <v>2256</v>
       </c>
-      <c r="H16" s="89">
+      <c r="H16" s="88">
         <v>2256</v>
       </c>
       <c r="I16" s="10"/>
@@ -1439,24 +3765,24 @@
       <c r="N16" s="6"/>
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A17" s="84" t="s">
+      <c r="A17" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="85">
+      <c r="B17" s="84">
         <v>45912</v>
       </c>
-      <c r="C17" s="86">
+      <c r="C17" s="85">
         <v>1000</v>
       </c>
-      <c r="D17" s="84"/>
-      <c r="E17" s="84"/>
-      <c r="F17" s="90">
+      <c r="D17" s="83"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="89">
         <v>0.36</v>
       </c>
-      <c r="G17" s="89">
+      <c r="G17" s="88">
         <v>360</v>
       </c>
-      <c r="H17" s="89">
+      <c r="H17" s="88">
         <v>324</v>
       </c>
       <c r="I17" s="10"/>
@@ -1467,24 +3793,24 @@
       <c r="N17" s="6"/>
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A18" s="84" t="s">
+      <c r="A18" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="B18" s="85">
+      <c r="B18" s="84">
         <v>45905</v>
       </c>
-      <c r="C18" s="86">
+      <c r="C18" s="85">
         <v>8000</v>
       </c>
-      <c r="D18" s="84"/>
-      <c r="E18" s="84"/>
-      <c r="F18" s="84">
+      <c r="D18" s="83"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="83">
         <v>0.8</v>
       </c>
-      <c r="G18" s="89">
+      <c r="G18" s="88">
         <v>6400</v>
       </c>
-      <c r="H18" s="89">
+      <c r="H18" s="88">
         <v>5760</v>
       </c>
       <c r="I18" s="10"/>
@@ -1495,24 +3821,24 @@
       <c r="N18" s="6"/>
     </row>
     <row r="19" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A19" s="84" t="s">
+      <c r="A19" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="85">
+      <c r="B19" s="84">
         <v>45915</v>
       </c>
-      <c r="C19" s="86">
+      <c r="C19" s="85">
         <v>50000</v>
       </c>
-      <c r="D19" s="84"/>
-      <c r="E19" s="84"/>
-      <c r="F19" s="93">
+      <c r="D19" s="83"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="92">
         <v>0.13250000000000001</v>
       </c>
-      <c r="G19" s="89">
+      <c r="G19" s="88">
         <v>6625</v>
       </c>
-      <c r="H19" s="89">
+      <c r="H19" s="88">
         <v>5962.5</v>
       </c>
       <c r="I19" s="10"/>
@@ -1523,24 +3849,24 @@
       <c r="N19" s="6"/>
     </row>
     <row r="20" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A20" s="84" t="s">
+      <c r="A20" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="85">
+      <c r="B20" s="84">
         <v>45905</v>
       </c>
-      <c r="C20" s="92">
+      <c r="C20" s="91">
         <v>25000</v>
       </c>
-      <c r="D20" s="84"/>
-      <c r="E20" s="84"/>
-      <c r="F20" s="93">
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="92">
         <v>0.17169999999999999</v>
       </c>
-      <c r="G20" s="89">
+      <c r="G20" s="88">
         <v>4292.5</v>
       </c>
-      <c r="H20" s="89">
+      <c r="H20" s="88">
         <v>3863.25</v>
       </c>
       <c r="I20" s="10"/>
@@ -1570,31 +3896,31 @@
       <c r="N21" s="6"/>
     </row>
     <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="84" t="s">
+      <c r="A22" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="85">
+      <c r="B22" s="84">
         <v>45903</v>
       </c>
-      <c r="C22" s="84">
+      <c r="C22" s="83">
         <v>5000</v>
       </c>
-      <c r="D22" s="84">
+      <c r="D22" s="83">
         <v>7.5</v>
       </c>
-      <c r="E22" s="89">
+      <c r="E22" s="88">
         <v>37583.06</v>
       </c>
-      <c r="F22" s="84">
+      <c r="F22" s="83">
         <v>8.3000000000000007</v>
       </c>
-      <c r="G22" s="89">
+      <c r="G22" s="88">
         <v>41408.080000000002</v>
       </c>
-      <c r="H22" s="89">
+      <c r="H22" s="88">
         <v>3825.02</v>
       </c>
-      <c r="I22" s="60"/>
+      <c r="I22" s="59"/>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
       <c r="L22" s="15"/>
@@ -1602,31 +3928,31 @@
       <c r="N22" s="6"/>
     </row>
     <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A23" s="84" t="s">
+      <c r="A23" s="83" t="s">
         <v>65</v>
       </c>
-      <c r="B23" s="85">
+      <c r="B23" s="84">
         <v>45908</v>
       </c>
-      <c r="C23" s="84">
+      <c r="C23" s="83">
         <v>5000</v>
       </c>
-      <c r="D23" s="84">
+      <c r="D23" s="83">
         <v>24.1</v>
       </c>
-      <c r="E23" s="89">
+      <c r="E23" s="88">
         <v>120766.9</v>
       </c>
-      <c r="F23" s="84">
+      <c r="F23" s="83">
         <v>23.4</v>
       </c>
-      <c r="G23" s="89">
+      <c r="G23" s="88">
         <v>116740.86</v>
       </c>
-      <c r="H23" s="89">
+      <c r="H23" s="88">
         <v>-4026.04</v>
       </c>
-      <c r="I23" s="60"/>
+      <c r="I23" s="59"/>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
       <c r="L23" s="15"/>
@@ -1634,31 +3960,31 @@
       <c r="N23" s="6"/>
     </row>
     <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A24" s="84" t="s">
+      <c r="A24" s="83" t="s">
         <v>65</v>
       </c>
-      <c r="B24" s="85">
+      <c r="B24" s="84">
         <v>45911</v>
       </c>
-      <c r="C24" s="84">
+      <c r="C24" s="83">
         <v>5000</v>
       </c>
-      <c r="D24" s="84">
+      <c r="D24" s="83">
         <v>23.2</v>
       </c>
-      <c r="E24" s="89">
+      <c r="E24" s="88">
         <v>116256.93</v>
       </c>
-      <c r="F24" s="84">
+      <c r="F24" s="83">
         <v>23.4</v>
       </c>
-      <c r="G24" s="89">
+      <c r="G24" s="88">
         <v>116740.86</v>
       </c>
-      <c r="H24" s="84">
+      <c r="H24" s="83">
         <v>483.93</v>
       </c>
-      <c r="I24" s="60"/>
+      <c r="I24" s="59"/>
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
       <c r="L24" s="15"/>
@@ -1666,31 +3992,31 @@
       <c r="N24" s="6"/>
     </row>
     <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A25" s="84" t="s">
+      <c r="A25" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="B25" s="85">
+      <c r="B25" s="84">
         <v>45915</v>
       </c>
-      <c r="C25" s="84">
+      <c r="C25" s="83">
         <v>4000</v>
       </c>
-      <c r="D25" s="84">
+      <c r="D25" s="83">
         <v>23.1</v>
       </c>
-      <c r="E25" s="89">
+      <c r="E25" s="88">
         <v>92604.66</v>
       </c>
-      <c r="F25" s="84">
+      <c r="F25" s="83">
         <v>25.75</v>
       </c>
-      <c r="G25" s="89">
+      <c r="G25" s="88">
         <v>102771.87</v>
       </c>
-      <c r="H25" s="89">
+      <c r="H25" s="88">
         <v>10167.209999999999</v>
       </c>
-      <c r="I25" s="60"/>
+      <c r="I25" s="59"/>
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
       <c r="L25" s="15"/>
@@ -1698,31 +4024,31 @@
       <c r="N25" s="6"/>
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A26" s="84" t="s">
+      <c r="A26" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="85">
+      <c r="B26" s="84">
         <v>45915</v>
       </c>
-      <c r="C26" s="84">
+      <c r="C26" s="83">
         <v>5000</v>
       </c>
-      <c r="D26" s="84">
+      <c r="D26" s="83">
         <v>8.8000000000000007</v>
       </c>
-      <c r="E26" s="89">
+      <c r="E26" s="88">
         <v>44097.46</v>
       </c>
-      <c r="F26" s="84">
+      <c r="F26" s="83">
         <v>9.6999999999999993</v>
       </c>
-      <c r="G26" s="89">
+      <c r="G26" s="88">
         <v>48392.57</v>
       </c>
-      <c r="H26" s="89">
+      <c r="H26" s="88">
         <v>4295.1099999999997</v>
       </c>
-      <c r="I26" s="60"/>
+      <c r="I26" s="59"/>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
       <c r="L26" s="15"/>
@@ -2053,2920 +4379,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32283096-5907-4E30-9E76-682BE04B55EC}">
-  <dimension ref="A1:N14"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.25" style="5" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.875" style="7" customWidth="1"/>
-    <col min="6" max="6" width="8" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16" style="7" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11" style="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.875" style="6" customWidth="1"/>
-    <col min="12" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="5"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="28">
-        <v>45288</v>
-      </c>
-      <c r="C2" s="29">
-        <v>22500</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="37">
-        <v>0</v>
-      </c>
-      <c r="G2" s="31">
-        <f t="shared" ref="G2" si="0">C2*F2</f>
-        <v>0</v>
-      </c>
-      <c r="H2" s="32">
-        <f>G2</f>
-        <v>0</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="32">
-        <f>SUM(H2,H2)</f>
-        <v>0</v>
-      </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="28">
-        <v>45295</v>
-      </c>
-      <c r="C4" s="29">
-        <v>2000</v>
-      </c>
-      <c r="D4" s="30">
-        <v>21.7</v>
-      </c>
-      <c r="E4" s="31">
-        <v>43496.13</v>
-      </c>
-      <c r="F4" s="30">
-        <v>22.9</v>
-      </c>
-      <c r="G4" s="31">
-        <v>45698.55</v>
-      </c>
-      <c r="H4" s="32">
-        <v>0</v>
-      </c>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="26"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="32">
-        <f>SUM(E4:E4)</f>
-        <v>43496.13</v>
-      </c>
-      <c r="F5" s="30"/>
-      <c r="G5" s="32">
-        <f>SUM(G4:G4)</f>
-        <v>45698.55</v>
-      </c>
-      <c r="H5" s="32">
-        <f>SUM(H4:H4)</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="15"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="26"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="34">
-        <f>H3+H5</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="32">
-        <v>308374.99525200005</v>
-      </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-    </row>
-    <row r="8" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="26"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="41">
-        <f>H6+H7</f>
-        <v>308374.99525200005</v>
-      </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-    </row>
-    <row r="9" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="26"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="35">
-        <v>0</v>
-      </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-    </row>
-    <row r="10" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="26"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="H10" s="35">
-        <v>43930</v>
-      </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="26"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="41">
-        <f>H9+H10</f>
-        <v>43930</v>
-      </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="5"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="36">
-        <f>H8-H11</f>
-        <v>264444.99525200005</v>
-      </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="5"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="H13" s="38">
-        <v>57000</v>
-      </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="6"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="H14" s="48">
-        <f>H12+H13</f>
-        <v>321444.99525200005</v>
-      </c>
-      <c r="I14" s="11"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70859943-B961-4C68-A873-2ACB6A8732BB}">
-  <dimension ref="A1:N28"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="14.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
-    <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="28">
-        <v>45632</v>
-      </c>
-      <c r="C2" s="29">
-        <v>35000</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="37">
-        <v>0.22220000000000001</v>
-      </c>
-      <c r="G2" s="31">
-        <f t="shared" ref="G2:G12" si="0">C2*F2</f>
-        <v>7777</v>
-      </c>
-      <c r="H2" s="40">
-        <f t="shared" ref="H2:H11" si="1">G2*0.9</f>
-        <v>6999.3</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A3" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="28">
-        <v>45632</v>
-      </c>
-      <c r="C3" s="29">
-        <v>27000</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="37">
-        <v>0.5</v>
-      </c>
-      <c r="G3" s="31">
-        <f t="shared" si="0"/>
-        <v>13500</v>
-      </c>
-      <c r="H3" s="40">
-        <f t="shared" si="1"/>
-        <v>12150</v>
-      </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A4" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="28">
-        <v>45637</v>
-      </c>
-      <c r="C4" s="29">
-        <v>7200</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="31"/>
-      <c r="F4" s="37">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="G4" s="31">
-        <f t="shared" si="0"/>
-        <v>1260</v>
-      </c>
-      <c r="H4" s="40">
-        <f t="shared" si="1"/>
-        <v>1134</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A5" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="28">
-        <v>45638</v>
-      </c>
-      <c r="C5" s="29">
-        <v>55000</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="37">
-        <v>0.2213</v>
-      </c>
-      <c r="G5" s="31">
-        <f t="shared" si="0"/>
-        <v>12171.5</v>
-      </c>
-      <c r="H5" s="40">
-        <f t="shared" si="1"/>
-        <v>10954.35</v>
-      </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A6" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="28">
-        <v>45638</v>
-      </c>
-      <c r="C6" s="29">
-        <v>3600</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="31"/>
-      <c r="F6" s="37">
-        <v>0.1</v>
-      </c>
-      <c r="G6" s="31">
-        <f t="shared" si="0"/>
-        <v>360</v>
-      </c>
-      <c r="H6" s="40">
-        <f t="shared" si="1"/>
-        <v>324</v>
-      </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="28">
-        <v>45639</v>
-      </c>
-      <c r="C7" s="29">
-        <v>12500</v>
-      </c>
-      <c r="D7" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="31"/>
-      <c r="F7" s="37">
-        <v>0.215</v>
-      </c>
-      <c r="G7" s="31">
-        <f t="shared" si="0"/>
-        <v>2687.5</v>
-      </c>
-      <c r="H7" s="40">
-        <f t="shared" si="1"/>
-        <v>2418.75</v>
-      </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="28">
-        <v>45639</v>
-      </c>
-      <c r="C8" s="29">
-        <v>50000</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="31"/>
-      <c r="F8" s="37">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="G8" s="31">
-        <f t="shared" si="0"/>
-        <v>1050</v>
-      </c>
-      <c r="H8" s="40">
-        <f t="shared" si="1"/>
-        <v>945</v>
-      </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A9" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="28">
-        <v>45639</v>
-      </c>
-      <c r="C9" s="29">
-        <v>20000</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="31"/>
-      <c r="F9" s="37">
-        <v>0.193</v>
-      </c>
-      <c r="G9" s="31">
-        <f t="shared" si="0"/>
-        <v>3860</v>
-      </c>
-      <c r="H9" s="40">
-        <f t="shared" si="1"/>
-        <v>3474</v>
-      </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="28">
-        <v>45643</v>
-      </c>
-      <c r="C10" s="29">
-        <v>50000</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="37">
-        <v>0.22289999999999999</v>
-      </c>
-      <c r="G10" s="31">
-        <f t="shared" si="0"/>
-        <v>11145</v>
-      </c>
-      <c r="H10" s="40">
-        <f t="shared" si="1"/>
-        <v>10030.5</v>
-      </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A11" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="28">
-        <v>45651</v>
-      </c>
-      <c r="C11" s="29">
-        <v>60000</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="37">
-        <v>0.19980000000000001</v>
-      </c>
-      <c r="G11" s="31">
-        <f t="shared" si="0"/>
-        <v>11988</v>
-      </c>
-      <c r="H11" s="40">
-        <f t="shared" si="1"/>
-        <v>10789.2</v>
-      </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="28">
-        <v>45653</v>
-      </c>
-      <c r="C12" s="29">
-        <v>20000</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="31"/>
-      <c r="F12" s="37">
-        <v>0.1192</v>
-      </c>
-      <c r="G12" s="31">
-        <f t="shared" si="0"/>
-        <v>2384</v>
-      </c>
-      <c r="H12" s="40">
-        <f>G12</f>
-        <v>2384</v>
-      </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="27"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="34">
-        <f>SUM(H2:H12)</f>
-        <v>61603.100000000006</v>
-      </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="28">
-        <v>37617</v>
-      </c>
-      <c r="C14" s="29">
-        <v>0</v>
-      </c>
-      <c r="D14" s="30">
-        <v>21.3</v>
-      </c>
-      <c r="E14" s="31">
-        <v>0</v>
-      </c>
-      <c r="F14" s="30">
-        <v>21.3</v>
-      </c>
-      <c r="G14" s="31">
-        <v>0</v>
-      </c>
-      <c r="H14" s="32">
-        <f t="shared" ref="H14" si="2">G14-E14</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="11"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="26"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="32">
-        <f>SUM(E14:E14)</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="30"/>
-      <c r="G15" s="32">
-        <f>SUM(G14:G14)</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="40">
-        <f>SUM(H14:H14)</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="7"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-    </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A16" s="26"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H16" s="34">
-        <f>H13+H15</f>
-        <v>61603.100000000006</v>
-      </c>
-      <c r="I16" s="11"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="6"/>
-    </row>
-    <row r="17" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="26"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H17" s="32">
-        <v>318141.89525200002</v>
-      </c>
-      <c r="K17" s="7"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-    </row>
-    <row r="18" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="26"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="H18" s="41">
-        <f>H16+H17</f>
-        <v>379744.99525200005</v>
-      </c>
-      <c r="K18" s="7"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-    </row>
-    <row r="19" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="26"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19" s="35">
-        <v>701370</v>
-      </c>
-      <c r="K19" s="7"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-    </row>
-    <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="26"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="H20" s="35">
-        <v>38000</v>
-      </c>
-      <c r="K20" s="7"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-    </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A21" s="26"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="41">
-        <f>H19+H20</f>
-        <v>739370</v>
-      </c>
-      <c r="I21" s="11"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="6"/>
-    </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="5"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H22" s="36">
-        <f>H18-H21</f>
-        <v>-359625.00474799995</v>
-      </c>
-      <c r="I22" s="11"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="6"/>
-    </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A23" s="5"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="H23" s="38">
-        <v>668000</v>
-      </c>
-      <c r="I23" s="11"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="6"/>
-    </row>
-    <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A24" s="6"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="H24" s="48">
-        <f>H22+H23</f>
-        <v>308374.99525200005</v>
-      </c>
-      <c r="I24" s="11"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="6"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="K25" s="7"/>
-      <c r="M25" s="7"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M26" s="7"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M27" s="7"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C28" s="12"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="10"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="7"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I12">
-    <sortCondition ref="B2:B12"/>
-    <sortCondition ref="A2:A12"/>
-  </sortState>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7988E558-09BF-4546-BFFB-0E642120F5F9}">
-  <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11.375" style="18" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="13.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
-    <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="28">
-        <v>44846</v>
-      </c>
-      <c r="C2" s="29">
-        <v>0</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="37">
-        <v>1.3</v>
-      </c>
-      <c r="G2" s="31">
-        <f>C2*F2</f>
-        <v>0</v>
-      </c>
-      <c r="H2" s="32">
-        <f>G2*0.9</f>
-        <v>0</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="34">
-        <f>SUM(H2:H2)</f>
-        <v>0</v>
-      </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="28">
-        <v>45590</v>
-      </c>
-      <c r="C4" s="29">
-        <v>1500</v>
-      </c>
-      <c r="D4" s="30">
-        <v>12</v>
-      </c>
-      <c r="E4" s="31">
-        <v>19756.14</v>
-      </c>
-      <c r="F4" s="30">
-        <v>0</v>
-      </c>
-      <c r="G4" s="31">
-        <v>19756.14</v>
-      </c>
-      <c r="H4" s="40">
-        <f>G4-E4</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="26"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="32">
-        <f>SUM(E4:E4)</f>
-        <v>19756.14</v>
-      </c>
-      <c r="F5" s="30"/>
-      <c r="G5" s="32">
-        <f>SUM(G4:G4)</f>
-        <v>19756.14</v>
-      </c>
-      <c r="H5" s="32">
-        <f>SUM(H4:H4)</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="7"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="26"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="43">
-        <f>H3+H5</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="32">
-        <v>318141.89525200002</v>
-      </c>
-      <c r="I7" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="7"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-    </row>
-    <row r="8" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="26"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="41">
-        <f>H6+H7</f>
-        <v>318141.89525200002</v>
-      </c>
-      <c r="K8" s="7"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-    </row>
-    <row r="9" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="26"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="35">
-        <v>675050</v>
-      </c>
-      <c r="I9" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="7"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-    </row>
-    <row r="10" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="26"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="H10" s="35">
-        <v>26320</v>
-      </c>
-      <c r="K10" s="7"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="26"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="41">
-        <f>H9+H10</f>
-        <v>701370</v>
-      </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="5"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="45">
-        <f>H8-H11</f>
-        <v>-383228.10474799998</v>
-      </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="5"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="H13" s="38">
-        <v>668000</v>
-      </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="6"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="H14" s="42">
-        <f>H12+H13</f>
-        <v>284771.89525200002</v>
-      </c>
-      <c r="I14" s="11"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="K15" s="7"/>
-      <c r="M15" s="7"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M16" s="7"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="M17" s="7"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C18" s="12"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="10"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="7"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9E8D5A8-C6BD-47CE-94D2-6F0DD38CBCC4}">
-  <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11.375" style="18" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
-    <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="28">
-        <v>45576</v>
-      </c>
-      <c r="C2" s="29">
-        <v>6800</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="55">
-        <v>0.24</v>
-      </c>
-      <c r="G2" s="31">
-        <f>C2*F2</f>
-        <v>1632</v>
-      </c>
-      <c r="H2" s="56">
-        <f>G2*0.9</f>
-        <v>1468.8</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="34">
-        <f>SUM(H2:H2)</f>
-        <v>1468.8</v>
-      </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="28">
-        <v>45590</v>
-      </c>
-      <c r="C4" s="29">
-        <v>1500</v>
-      </c>
-      <c r="D4" s="30">
-        <v>12</v>
-      </c>
-      <c r="E4" s="31">
-        <v>19756.14</v>
-      </c>
-      <c r="F4" s="30">
-        <v>0</v>
-      </c>
-      <c r="G4" s="31">
-        <v>19756.14</v>
-      </c>
-      <c r="H4" s="40">
-        <f>G4-E4</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="26"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="32">
-        <f>SUM(E4:E4)</f>
-        <v>19756.14</v>
-      </c>
-      <c r="F5" s="30"/>
-      <c r="G5" s="32">
-        <f>SUM(G4:G4)</f>
-        <v>19756.14</v>
-      </c>
-      <c r="H5" s="40">
-        <f>SUM(H4:H4)</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="7"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="26"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="34">
-        <f>H3+H5</f>
-        <v>1468.8</v>
-      </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="32">
-        <v>316673.09525200003</v>
-      </c>
-      <c r="K7" s="7"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-    </row>
-    <row r="8" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="26"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="41">
-        <f>H6+H7</f>
-        <v>318141.89525200002</v>
-      </c>
-      <c r="K8" s="7"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-    </row>
-    <row r="9" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="26"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="35">
-        <v>614170</v>
-      </c>
-      <c r="K9" s="7"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-    </row>
-    <row r="10" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="26"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="H10" s="35">
-        <v>60880</v>
-      </c>
-      <c r="K10" s="7"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="26"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="41">
-        <f>H9+H10</f>
-        <v>675050</v>
-      </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="5"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="45">
-        <f>H8-H11</f>
-        <v>-356908.10474799998</v>
-      </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="5"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="H13" s="38">
-        <v>668000</v>
-      </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="6"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="H14" s="42">
-        <f>H12+H13</f>
-        <v>311091.89525200002</v>
-      </c>
-      <c r="I14" s="11"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="K15" s="7"/>
-      <c r="M15" s="7"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M16" s="7"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="M17" s="7"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C18" s="12"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="10"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="7"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E04FE74-71A4-490B-8947-83CEB1364CED}">
-  <dimension ref="A1:N41"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.125" style="10" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
-    <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="59"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="28">
-        <v>45540</v>
-      </c>
-      <c r="C2" s="29">
-        <v>30000</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="54">
-        <v>0.22220000000000001</v>
-      </c>
-      <c r="G2" s="31">
-        <f t="shared" ref="G2:G20" si="0">C2*F2</f>
-        <v>6666</v>
-      </c>
-      <c r="H2" s="56">
-        <f>G2*0.9</f>
-        <v>5999.4000000000005</v>
-      </c>
-      <c r="I2" s="10"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A3" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="28">
-        <v>45540</v>
-      </c>
-      <c r="C3" s="29">
-        <v>7500</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="55">
-        <v>0.38</v>
-      </c>
-      <c r="G3" s="31">
-        <f t="shared" si="0"/>
-        <v>2850</v>
-      </c>
-      <c r="H3" s="56">
-        <f>G3*0.9</f>
-        <v>2565</v>
-      </c>
-      <c r="I3" s="10"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A4" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="28">
-        <v>45541</v>
-      </c>
-      <c r="C4" s="29">
-        <v>27000</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="31"/>
-      <c r="F4" s="37">
-        <v>0.05</v>
-      </c>
-      <c r="G4" s="31">
-        <f t="shared" si="0"/>
-        <v>1350</v>
-      </c>
-      <c r="H4" s="56">
-        <f>G4</f>
-        <v>1350</v>
-      </c>
-      <c r="I4" s="10"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A5" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="28">
-        <v>45541</v>
-      </c>
-      <c r="C5" s="29">
-        <v>27000</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="55">
-        <v>0.5</v>
-      </c>
-      <c r="G5" s="31">
-        <f t="shared" si="0"/>
-        <v>13500</v>
-      </c>
-      <c r="H5" s="56">
-        <f>G5*0.9</f>
-        <v>12150</v>
-      </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A6" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="28">
-        <v>45541</v>
-      </c>
-      <c r="C6" s="29">
-        <v>36000</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="31"/>
-      <c r="F6" s="54">
-        <v>0.05</v>
-      </c>
-      <c r="G6" s="31">
-        <f t="shared" si="0"/>
-        <v>1800</v>
-      </c>
-      <c r="H6" s="56">
-        <f>G6*0.9</f>
-        <v>1620</v>
-      </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="28">
-        <v>45541</v>
-      </c>
-      <c r="C7" s="29">
-        <v>30000</v>
-      </c>
-      <c r="D7" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="31"/>
-      <c r="F7" s="37">
-        <v>0.193</v>
-      </c>
-      <c r="G7" s="31">
-        <f t="shared" si="0"/>
-        <v>5790</v>
-      </c>
-      <c r="H7" s="56">
-        <f>G7*0.9</f>
-        <v>5211</v>
-      </c>
-      <c r="I7" s="10"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="28">
-        <v>45545</v>
-      </c>
-      <c r="C8" s="29">
-        <v>78000</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="31"/>
-      <c r="F8" s="55">
-        <v>0.2</v>
-      </c>
-      <c r="G8" s="31">
-        <f t="shared" si="0"/>
-        <v>15600</v>
-      </c>
-      <c r="H8" s="32">
-        <f>G8</f>
-        <v>15600</v>
-      </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A9" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="28">
-        <v>45545</v>
-      </c>
-      <c r="C9" s="29">
-        <v>15000</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="31"/>
-      <c r="F9" s="37">
-        <v>0.1</v>
-      </c>
-      <c r="G9" s="31">
-        <f t="shared" si="0"/>
-        <v>1500</v>
-      </c>
-      <c r="H9" s="32">
-        <f>G9*0.9</f>
-        <v>1350</v>
-      </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="28">
-        <v>45546</v>
-      </c>
-      <c r="C10" s="29">
-        <v>1200</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="54">
-        <v>0.3</v>
-      </c>
-      <c r="G10" s="31">
-        <f t="shared" si="0"/>
-        <v>360</v>
-      </c>
-      <c r="H10" s="32">
-        <v>328.8</v>
-      </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A11" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="28">
-        <v>45546</v>
-      </c>
-      <c r="C11" s="29">
-        <v>60000</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="54">
-        <v>3.9899999999999998E-2</v>
-      </c>
-      <c r="G11" s="31">
-        <f t="shared" si="0"/>
-        <v>2394</v>
-      </c>
-      <c r="H11" s="56">
-        <f>G11*0.9</f>
-        <v>2154.6</v>
-      </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="28">
-        <v>45546</v>
-      </c>
-      <c r="C12" s="29">
-        <v>10000</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="31"/>
-      <c r="F12" s="37">
-        <v>0.6</v>
-      </c>
-      <c r="G12" s="31">
-        <f t="shared" si="0"/>
-        <v>6000</v>
-      </c>
-      <c r="H12" s="56">
-        <v>5520</v>
-      </c>
-      <c r="I12" s="10"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="28">
-        <v>45547</v>
-      </c>
-      <c r="C13" s="29">
-        <v>12500</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="31"/>
-      <c r="F13" s="54">
-        <v>0.14330000000000001</v>
-      </c>
-      <c r="G13" s="31">
-        <f t="shared" si="0"/>
-        <v>1791.2500000000002</v>
-      </c>
-      <c r="H13" s="32">
-        <f>G13*0.9</f>
-        <v>1612.1250000000002</v>
-      </c>
-      <c r="I13" s="10"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A14" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="28">
-        <v>45547</v>
-      </c>
-      <c r="C14" s="29">
-        <v>30000</v>
-      </c>
-      <c r="D14" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="31"/>
-      <c r="F14" s="54">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G14" s="31">
-        <f t="shared" si="0"/>
-        <v>2100</v>
-      </c>
-      <c r="H14" s="32">
-        <f>G14*0.9</f>
-        <v>1890</v>
-      </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A15" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="28">
-        <v>45547</v>
-      </c>
-      <c r="C15" s="29">
-        <v>4000</v>
-      </c>
-      <c r="D15" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="31"/>
-      <c r="F15" s="55">
-        <v>0.12</v>
-      </c>
-      <c r="G15" s="31">
-        <f t="shared" si="0"/>
-        <v>480</v>
-      </c>
-      <c r="H15" s="32">
-        <f>G15*0.9</f>
-        <v>432</v>
-      </c>
-      <c r="I15" s="10"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="6"/>
-    </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A16" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="28">
-        <v>45547</v>
-      </c>
-      <c r="C16" s="29">
-        <v>66000</v>
-      </c>
-      <c r="D16" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="31"/>
-      <c r="F16" s="54">
-        <v>0.1963</v>
-      </c>
-      <c r="G16" s="31">
-        <f t="shared" si="0"/>
-        <v>12955.8</v>
-      </c>
-      <c r="H16" s="32">
-        <f>G16*0.9</f>
-        <v>11660.22</v>
-      </c>
-      <c r="I16" s="10"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="6"/>
-    </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A17" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="28">
-        <v>45547</v>
-      </c>
-      <c r="C17" s="29">
-        <v>8000</v>
-      </c>
-      <c r="D17" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="31"/>
-      <c r="F17" s="54">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="G17" s="31">
-        <f t="shared" si="0"/>
-        <v>1400</v>
-      </c>
-      <c r="H17" s="32">
-        <f>G17*0.9</f>
-        <v>1260</v>
-      </c>
-      <c r="I17" s="10"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="6"/>
-    </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A18" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="28">
-        <v>45548</v>
-      </c>
-      <c r="C18" s="29">
-        <v>20000</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="31"/>
-      <c r="F18" s="55">
-        <v>0.11020000000000001</v>
-      </c>
-      <c r="G18" s="31">
-        <f t="shared" si="0"/>
-        <v>2204</v>
-      </c>
-      <c r="H18" s="32">
-        <f>G18</f>
-        <v>2204</v>
-      </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="6"/>
-    </row>
-    <row r="19" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A19" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19" s="28">
-        <v>45548</v>
-      </c>
-      <c r="C19" s="29">
-        <v>1000</v>
-      </c>
-      <c r="D19" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="31"/>
-      <c r="F19" s="58">
-        <v>0.33</v>
-      </c>
-      <c r="G19" s="31">
-        <f t="shared" si="0"/>
-        <v>330</v>
-      </c>
-      <c r="H19" s="32">
-        <f>G19*0.9</f>
-        <v>297</v>
-      </c>
-      <c r="I19" s="10"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="6"/>
-    </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A20" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="28">
-        <v>45559</v>
-      </c>
-      <c r="C20" s="29">
-        <v>50000</v>
-      </c>
-      <c r="D20" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" s="31"/>
-      <c r="F20" s="55">
-        <v>0.13719999999999999</v>
-      </c>
-      <c r="G20" s="31">
-        <f t="shared" si="0"/>
-        <v>6859.9999999999991</v>
-      </c>
-      <c r="H20" s="32">
-        <f>G20*0.9</f>
-        <v>6173.9999999999991</v>
-      </c>
-      <c r="I20" s="10"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="6"/>
-    </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A21" s="27"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="34">
-        <f>SUM(H2:H20)</f>
-        <v>79378.145000000004</v>
-      </c>
-      <c r="I21" s="10"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="6"/>
-    </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="28">
-        <v>45541</v>
-      </c>
-      <c r="C22" s="29">
-        <v>3000</v>
-      </c>
-      <c r="D22" s="30">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="E22" s="31">
-        <v>13830.565619999999</v>
-      </c>
-      <c r="F22" s="30">
-        <v>5.6</v>
-      </c>
-      <c r="G22" s="31">
-        <v>16762.645872000001</v>
-      </c>
-      <c r="H22" s="32">
-        <f t="shared" ref="H22:H27" si="1">G22-E22</f>
-        <v>2932.0802520000016</v>
-      </c>
-      <c r="I22" s="60"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="6"/>
-    </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A23" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="28">
-        <v>45545</v>
-      </c>
-      <c r="C23" s="29">
-        <v>5000</v>
-      </c>
-      <c r="D23" s="30">
-        <v>12.6</v>
-      </c>
-      <c r="E23" s="31">
-        <v>63139.54</v>
-      </c>
-      <c r="F23" s="30">
-        <v>12.7</v>
-      </c>
-      <c r="G23" s="31">
-        <v>63359.35</v>
-      </c>
-      <c r="H23" s="32">
-        <f t="shared" si="1"/>
-        <v>219.80999999999767</v>
-      </c>
-      <c r="I23" s="60"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="6"/>
-    </row>
-    <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A24" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" s="28">
-        <v>45551</v>
-      </c>
-      <c r="C24" s="29">
-        <v>800</v>
-      </c>
-      <c r="D24" s="30">
-        <v>20</v>
-      </c>
-      <c r="E24" s="31">
-        <v>16035.44</v>
-      </c>
-      <c r="F24" s="30">
-        <v>23.9</v>
-      </c>
-      <c r="G24" s="31">
-        <v>19077.650000000001</v>
-      </c>
-      <c r="H24" s="32">
-        <f t="shared" si="1"/>
-        <v>3042.2100000000009</v>
-      </c>
-      <c r="I24" s="60"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="6"/>
-    </row>
-    <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A25" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" s="28">
-        <v>45554</v>
-      </c>
-      <c r="C25" s="29">
-        <v>6000</v>
-      </c>
-      <c r="D25" s="30">
-        <v>6</v>
-      </c>
-      <c r="E25" s="31">
-        <v>36079.74</v>
-      </c>
-      <c r="F25" s="30">
-        <v>6.95</v>
-      </c>
-      <c r="G25" s="31">
-        <v>41607.64</v>
-      </c>
-      <c r="H25" s="32">
-        <f t="shared" si="1"/>
-        <v>5527.9000000000015</v>
-      </c>
-      <c r="I25" s="60"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="6"/>
-    </row>
-    <row r="26" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A26" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="B26" s="28">
-        <v>45555</v>
-      </c>
-      <c r="C26" s="29">
-        <v>10000</v>
-      </c>
-      <c r="D26" s="30">
-        <v>9.15</v>
-      </c>
-      <c r="E26" s="31">
-        <v>91702.67</v>
-      </c>
-      <c r="F26" s="30">
-        <v>6.5</v>
-      </c>
-      <c r="G26" s="31">
-        <v>64856.03</v>
-      </c>
-      <c r="H26" s="32">
-        <f t="shared" si="1"/>
-        <v>-26846.639999999999</v>
-      </c>
-      <c r="I26" s="60"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="6"/>
-    </row>
-    <row r="27" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A27" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="28">
-        <v>45560</v>
-      </c>
-      <c r="C27" s="29">
-        <v>3000</v>
-      </c>
-      <c r="D27" s="30">
-        <v>7.6</v>
-      </c>
-      <c r="E27" s="31">
-        <v>22850.5</v>
-      </c>
-      <c r="F27" s="30">
-        <v>8.0500000000000007</v>
-      </c>
-      <c r="G27" s="31">
-        <v>24096.51</v>
-      </c>
-      <c r="H27" s="32">
-        <f t="shared" si="1"/>
-        <v>1246.0099999999984</v>
-      </c>
-      <c r="I27" s="60"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="6"/>
-    </row>
-    <row r="28" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="26"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="32">
-        <f>SUM(E22:E27)</f>
-        <v>243638.45562000002</v>
-      </c>
-      <c r="F28" s="30"/>
-      <c r="G28" s="32">
-        <f>SUM(G22:G27)</f>
-        <v>229759.82587199999</v>
-      </c>
-      <c r="H28" s="32">
-        <f>SUM(H22:H27)</f>
-        <v>-13878.629747999999</v>
-      </c>
-      <c r="I28" s="32"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-    </row>
-    <row r="29" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A29" s="26"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H29" s="34">
-        <f>H21+H28</f>
-        <v>65499.515252000005</v>
-      </c>
-      <c r="I29" s="10"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="6"/>
-    </row>
-    <row r="30" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="26"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H30" s="32">
-        <v>251173.58000000005</v>
-      </c>
-      <c r="K30" s="7"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-    </row>
-    <row r="31" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="26"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="H31" s="41">
-        <f>H29+H30</f>
-        <v>316673.09525200003</v>
-      </c>
-      <c r="K31" s="7"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-    </row>
-    <row r="32" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="26"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H32" s="35">
-        <v>574170</v>
-      </c>
-      <c r="K32" s="7"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-    </row>
-    <row r="33" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="26"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="H33" s="35">
-        <v>24140</v>
-      </c>
-      <c r="K33" s="7"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
-    </row>
-    <row r="34" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="26"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="29"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" s="41">
-        <f>H32+H33</f>
-        <v>598310</v>
-      </c>
-      <c r="I34" s="10"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="6"/>
-    </row>
-    <row r="35" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A35" s="5"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H35" s="45">
-        <f>H31-H34</f>
-        <v>-281636.90474799997</v>
-      </c>
-      <c r="I35" s="10"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="6"/>
-    </row>
-    <row r="36" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A36" s="5"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="H36" s="38">
-        <v>668000</v>
-      </c>
-      <c r="I36" s="10"/>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="6"/>
-    </row>
-    <row r="37" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A37" s="6"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="H37" s="42">
-        <f>H35+H36</f>
-        <v>386363.09525200003</v>
-      </c>
-      <c r="I37" s="10"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="15"/>
-      <c r="M37" s="15"/>
-      <c r="N37" s="6"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="K38" s="7"/>
-      <c r="M38" s="7"/>
-    </row>
-    <row r="39" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="B39" s="28">
-        <v>45546</v>
-      </c>
-      <c r="C39" s="29">
-        <v>24000</v>
-      </c>
-      <c r="D39" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" s="31"/>
-      <c r="F39" s="54">
-        <v>3.9899999999999998E-2</v>
-      </c>
-      <c r="G39" s="31">
-        <f>C39*F39</f>
-        <v>957.59999999999991</v>
-      </c>
-      <c r="H39" s="56">
-        <f>G39*0.9</f>
-        <v>861.83999999999992</v>
-      </c>
-      <c r="K39" s="7"/>
-      <c r="L39" s="15"/>
-      <c r="M39" s="15"/>
-    </row>
-    <row r="40" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="57" t="s">
-        <v>54</v>
-      </c>
-      <c r="B40" s="28">
-        <v>45530</v>
-      </c>
-      <c r="C40" s="29">
-        <v>30000</v>
-      </c>
-      <c r="D40" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" s="31"/>
-      <c r="F40" s="37">
-        <v>0.19</v>
-      </c>
-      <c r="G40" s="31">
-        <f>C40*F40</f>
-        <v>5700</v>
-      </c>
-      <c r="H40" s="32">
-        <f>G40</f>
-        <v>5700</v>
-      </c>
-      <c r="K40" s="7"/>
-      <c r="L40" s="15"/>
-      <c r="M40" s="15"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C41" s="12"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="10"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="7"/>
-      <c r="L41" s="6"/>
-      <c r="M41" s="7"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A13:N17">
-    <sortCondition ref="A13:A17"/>
-  </sortState>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{961B3AB4-C9A4-46F9-AED6-DC61A66CC09A}">
   <dimension ref="A1:N29"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -5034,7 +4447,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="31"/>
-      <c r="F2" s="82">
+      <c r="F2" s="81">
         <v>2.5</v>
       </c>
       <c r="G2" s="31">
@@ -5072,28 +4485,28 @@
       <c r="N3" s="6"/>
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="84" t="s">
+      <c r="A4" s="83" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="85">
+      <c r="B4" s="84">
         <v>45874</v>
       </c>
-      <c r="C4" s="86">
+      <c r="C4" s="85">
         <v>10000</v>
       </c>
-      <c r="D4" s="87">
+      <c r="D4" s="86">
         <v>1.88</v>
       </c>
-      <c r="E4" s="87">
+      <c r="E4" s="86">
         <v>18841.64</v>
       </c>
-      <c r="F4" s="87">
+      <c r="F4" s="86">
         <v>1.9</v>
       </c>
-      <c r="G4" s="87">
+      <c r="G4" s="86">
         <v>18957.919999999998</v>
       </c>
-      <c r="H4" s="87">
+      <c r="H4" s="86">
         <v>116.28</v>
       </c>
       <c r="I4" s="11"/>
@@ -5104,28 +4517,28 @@
       <c r="N4" s="6"/>
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A5" s="84" t="s">
+      <c r="A5" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="85">
+      <c r="B5" s="84">
         <v>45875</v>
       </c>
-      <c r="C5" s="86">
+      <c r="C5" s="85">
         <v>2800</v>
       </c>
-      <c r="D5" s="87">
+      <c r="D5" s="86">
         <v>10.5</v>
       </c>
-      <c r="E5" s="87">
+      <c r="E5" s="86">
         <v>29465.119999999999</v>
       </c>
-      <c r="F5" s="87">
+      <c r="F5" s="86">
         <v>11.6</v>
       </c>
-      <c r="G5" s="87">
+      <c r="G5" s="86">
         <v>32408.06</v>
       </c>
-      <c r="H5" s="87">
+      <c r="H5" s="86">
         <v>2942.94</v>
       </c>
       <c r="I5" s="11"/>
@@ -5136,28 +4549,28 @@
       <c r="N5" s="6"/>
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="84" t="s">
+      <c r="A6" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="85">
+      <c r="B6" s="84">
         <v>45875</v>
       </c>
-      <c r="C6" s="86">
+      <c r="C6" s="85">
         <v>5000</v>
       </c>
-      <c r="D6" s="87">
+      <c r="D6" s="86">
         <v>3.9</v>
       </c>
-      <c r="E6" s="87">
+      <c r="E6" s="86">
         <v>19543.2</v>
       </c>
-      <c r="F6" s="87">
+      <c r="F6" s="86">
         <v>4.5199999999999996</v>
       </c>
-      <c r="G6" s="87">
+      <c r="G6" s="86">
         <v>22549.95</v>
       </c>
-      <c r="H6" s="87">
+      <c r="H6" s="86">
         <v>3006.75</v>
       </c>
       <c r="I6" s="11"/>
@@ -5168,28 +4581,28 @@
       <c r="N6" s="6"/>
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="84" t="s">
+      <c r="A7" s="83" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="85">
+      <c r="B7" s="84">
         <v>45876</v>
       </c>
-      <c r="C7" s="86">
+      <c r="C7" s="85">
         <v>3200</v>
       </c>
-      <c r="D7" s="87">
+      <c r="D7" s="86">
         <v>9.25</v>
       </c>
-      <c r="E7" s="87">
+      <c r="E7" s="86">
         <v>29665.56</v>
       </c>
-      <c r="F7" s="87">
+      <c r="F7" s="86">
         <v>9.4</v>
       </c>
-      <c r="G7" s="87">
+      <c r="G7" s="86">
         <v>30013.37</v>
       </c>
-      <c r="H7" s="87">
+      <c r="H7" s="86">
         <v>347.81</v>
       </c>
       <c r="I7" s="11"/>
@@ -5200,28 +4613,28 @@
       <c r="N7" s="6"/>
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="84" t="s">
+      <c r="A8" s="83" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="85">
+      <c r="B8" s="84">
         <v>45876</v>
       </c>
-      <c r="C8" s="86">
+      <c r="C8" s="85">
         <v>10000</v>
       </c>
-      <c r="D8" s="87">
+      <c r="D8" s="86">
         <v>1.85</v>
       </c>
-      <c r="E8" s="87">
+      <c r="E8" s="86">
         <v>18540.98</v>
       </c>
-      <c r="F8" s="87">
+      <c r="F8" s="86">
         <v>2.06</v>
       </c>
-      <c r="G8" s="87">
+      <c r="G8" s="86">
         <v>20554.38</v>
       </c>
-      <c r="H8" s="87">
+      <c r="H8" s="86">
         <v>2013.4</v>
       </c>
       <c r="I8" s="11"/>
@@ -5232,28 +4645,28 @@
       <c r="N8" s="6"/>
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="84" t="s">
+      <c r="A9" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="85">
+      <c r="B9" s="84">
         <v>45877</v>
       </c>
-      <c r="C9" s="86">
+      <c r="C9" s="85">
         <v>6000</v>
       </c>
-      <c r="D9" s="87">
+      <c r="D9" s="86">
         <v>6.1</v>
       </c>
-      <c r="E9" s="87">
+      <c r="E9" s="86">
         <v>36681.06</v>
       </c>
-      <c r="F9" s="87">
+      <c r="F9" s="86">
         <v>6.7</v>
       </c>
-      <c r="G9" s="87">
+      <c r="G9" s="86">
         <v>40110.97</v>
       </c>
-      <c r="H9" s="87">
+      <c r="H9" s="86">
         <v>3429.91</v>
       </c>
       <c r="I9" s="11"/>
@@ -5264,31 +4677,31 @@
       <c r="N9" s="6"/>
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="84" t="s">
+      <c r="A10" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="85">
+      <c r="B10" s="84">
         <v>45877</v>
       </c>
-      <c r="C10" s="86">
+      <c r="C10" s="85">
         <v>3000</v>
       </c>
-      <c r="D10" s="87">
+      <c r="D10" s="86">
         <v>27.75</v>
       </c>
-      <c r="E10" s="87">
+      <c r="E10" s="86">
         <v>83434.39</v>
       </c>
-      <c r="F10" s="87">
+      <c r="F10" s="86">
         <v>31</v>
       </c>
-      <c r="G10" s="87">
+      <c r="G10" s="86">
         <v>92794.01</v>
       </c>
-      <c r="H10" s="87">
+      <c r="H10" s="86">
         <v>9359.6200000000008</v>
       </c>
-      <c r="I10" s="83"/>
+      <c r="I10" s="82"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="15"/>
@@ -5296,28 +4709,28 @@
       <c r="N10" s="6"/>
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="84" t="s">
+      <c r="A11" s="83" t="s">
         <v>65</v>
       </c>
-      <c r="B11" s="85">
+      <c r="B11" s="84">
         <v>45889</v>
       </c>
-      <c r="C11" s="86">
+      <c r="C11" s="85">
         <v>4000</v>
       </c>
-      <c r="D11" s="87">
+      <c r="D11" s="86">
         <v>24.1</v>
       </c>
-      <c r="E11" s="87">
+      <c r="E11" s="86">
         <v>96613.52</v>
       </c>
-      <c r="F11" s="87">
+      <c r="F11" s="86">
         <v>24.3</v>
       </c>
-      <c r="G11" s="87">
+      <c r="G11" s="86">
         <v>96984.72</v>
       </c>
-      <c r="H11" s="87">
+      <c r="H11" s="86">
         <v>371.2</v>
       </c>
       <c r="J11" s="7"/>
@@ -5327,28 +4740,28 @@
       <c r="N11" s="6"/>
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="84" t="s">
+      <c r="A12" s="83" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="85">
+      <c r="B12" s="84">
         <v>45890</v>
       </c>
-      <c r="C12" s="86">
+      <c r="C12" s="85">
         <v>4000</v>
       </c>
-      <c r="D12" s="87">
+      <c r="D12" s="86">
         <v>24.1</v>
       </c>
-      <c r="E12" s="87">
+      <c r="E12" s="86">
         <v>96613.52</v>
       </c>
-      <c r="F12" s="87">
+      <c r="F12" s="86">
         <v>24.3</v>
       </c>
-      <c r="G12" s="87">
+      <c r="G12" s="86">
         <v>96984.72</v>
       </c>
-      <c r="H12" s="87">
+      <c r="H12" s="86">
         <v>371.2</v>
       </c>
       <c r="J12" s="7"/>
@@ -5358,28 +4771,28 @@
       <c r="N12" s="6"/>
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="84" t="s">
+      <c r="A13" s="83" t="s">
         <v>65</v>
       </c>
-      <c r="B13" s="85">
+      <c r="B13" s="84">
         <v>45891</v>
       </c>
-      <c r="C13" s="86">
+      <c r="C13" s="85">
         <v>5000</v>
       </c>
-      <c r="D13" s="87">
+      <c r="D13" s="86">
         <v>24.1</v>
       </c>
-      <c r="E13" s="87">
+      <c r="E13" s="86">
         <v>120766.9</v>
       </c>
-      <c r="F13" s="87">
+      <c r="F13" s="86">
         <v>24.3</v>
       </c>
-      <c r="G13" s="87">
+      <c r="G13" s="86">
         <v>121230.88</v>
       </c>
-      <c r="H13" s="87">
+      <c r="H13" s="86">
         <v>463.98</v>
       </c>
       <c r="J13" s="7"/>
@@ -5389,28 +4802,28 @@
       <c r="N13" s="6"/>
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="84" t="s">
+      <c r="A14" s="83" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="85">
+      <c r="B14" s="84">
         <v>45896</v>
       </c>
-      <c r="C14" s="86">
+      <c r="C14" s="85">
         <v>6000</v>
       </c>
-      <c r="D14" s="87">
+      <c r="D14" s="86">
         <v>7.3</v>
       </c>
-      <c r="E14" s="87">
+      <c r="E14" s="86">
         <v>43897.02</v>
       </c>
-      <c r="F14" s="87">
+      <c r="F14" s="86">
         <v>8.4</v>
       </c>
-      <c r="G14" s="87">
+      <c r="G14" s="86">
         <v>50288.37</v>
       </c>
-      <c r="H14" s="87">
+      <c r="H14" s="86">
         <v>6391.35</v>
       </c>
       <c r="J14" s="7"/>
@@ -5420,31 +4833,31 @@
       <c r="N14" s="6"/>
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="84" t="s">
+      <c r="A15" s="83" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="85">
+      <c r="B15" s="84">
         <v>45897</v>
       </c>
-      <c r="C15" s="86">
+      <c r="C15" s="85">
         <v>5000</v>
       </c>
-      <c r="D15" s="87">
+      <c r="D15" s="86">
         <v>2.2000000000000002</v>
       </c>
-      <c r="E15" s="87">
+      <c r="E15" s="86">
         <v>11024.36</v>
       </c>
-      <c r="F15" s="87">
+      <c r="F15" s="86">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G15" s="87">
+      <c r="G15" s="86">
         <v>11474.52</v>
       </c>
-      <c r="H15" s="87">
+      <c r="H15" s="86">
         <v>450.16</v>
       </c>
-      <c r="I15" s="88"/>
+      <c r="I15" s="87"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
       <c r="L15" s="15"/>
@@ -5719,7 +5132,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7193655-9E82-4E5C-9879-086AA4339AB9}">
   <dimension ref="A1:N26"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -6393,7 +5806,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EAFE1F0-60EA-46C8-9C11-E7180F21BFAA}">
   <dimension ref="A1:N29"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -7100,13 +6513,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1E1A231-79A5-4BE4-8C0C-F5E13A4831EB}">
   <dimension ref="A1:N35"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="81" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="80" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
     <col min="5" max="5" width="14.375" style="7" bestFit="1" customWidth="1"/>
@@ -7126,7 +6539,7 @@
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="78" t="s">
+      <c r="B1" s="77" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="22" t="s">
@@ -7147,7 +6560,7 @@
       <c r="H1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="77"/>
+      <c r="I1" s="76"/>
       <c r="J1" s="3"/>
       <c r="K1" s="5"/>
       <c r="L1" s="7"/>
@@ -7158,7 +6571,7 @@
       <c r="A2" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="79">
+      <c r="B2" s="78">
         <v>45784</v>
       </c>
       <c r="C2" s="29">
@@ -7191,7 +6604,7 @@
       <c r="A3" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="79">
+      <c r="B3" s="78">
         <v>45785</v>
       </c>
       <c r="C3" s="29">
@@ -7224,7 +6637,7 @@
       <c r="A4" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="79">
+      <c r="B4" s="78">
         <v>45786</v>
       </c>
       <c r="C4" s="29">
@@ -7257,7 +6670,7 @@
       <c r="A5" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="79">
+      <c r="B5" s="78">
         <v>45786</v>
       </c>
       <c r="C5" s="29">
@@ -7290,7 +6703,7 @@
       <c r="A6" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="79">
+      <c r="B6" s="78">
         <v>45791</v>
       </c>
       <c r="C6" s="29">
@@ -7323,7 +6736,7 @@
       <c r="A7" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="79">
+      <c r="B7" s="78">
         <v>45793</v>
       </c>
       <c r="C7" s="29">
@@ -7356,7 +6769,7 @@
       <c r="A8" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="79">
+      <c r="B8" s="78">
         <v>45793</v>
       </c>
       <c r="C8" s="29">
@@ -7389,7 +6802,7 @@
       <c r="A9" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="B9" s="79">
+      <c r="B9" s="78">
         <v>45793</v>
       </c>
       <c r="C9" s="29">
@@ -7401,7 +6814,7 @@
       <c r="E9" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="76">
+      <c r="F9" s="75">
         <v>0.93</v>
       </c>
       <c r="G9" s="31">
@@ -7422,7 +6835,7 @@
       <c r="A10" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="79">
+      <c r="B10" s="78">
         <v>45797</v>
       </c>
       <c r="C10" s="29">
@@ -7455,7 +6868,7 @@
       <c r="A11" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="79">
+      <c r="B11" s="78">
         <v>45800</v>
       </c>
       <c r="C11" s="29">
@@ -7488,7 +6901,7 @@
       <c r="A12" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="79">
+      <c r="B12" s="78">
         <v>45800</v>
       </c>
       <c r="C12" s="29">
@@ -7521,7 +6934,7 @@
       <c r="A13" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="79">
+      <c r="B13" s="78">
         <v>45800</v>
       </c>
       <c r="C13" s="29">
@@ -7554,7 +6967,7 @@
       <c r="A14" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="79">
+      <c r="B14" s="78">
         <v>45800</v>
       </c>
       <c r="C14" s="29">
@@ -7586,7 +6999,7 @@
       <c r="A15" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="B15" s="79">
+      <c r="B15" s="78">
         <v>45800</v>
       </c>
       <c r="C15" s="29">
@@ -7619,7 +7032,7 @@
       <c r="A16" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="79">
+      <c r="B16" s="78">
         <v>45805</v>
       </c>
       <c r="C16" s="29">
@@ -7652,7 +7065,7 @@
       <c r="A17" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="79">
+      <c r="B17" s="78">
         <v>45806</v>
       </c>
       <c r="C17" s="29">
@@ -7683,7 +7096,7 @@
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A18" s="27"/>
-      <c r="B18" s="80"/>
+      <c r="B18" s="79"/>
       <c r="C18" s="29"/>
       <c r="D18" s="30"/>
       <c r="E18" s="31"/>
@@ -7704,7 +7117,7 @@
       <c r="A19" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="80">
+      <c r="B19" s="79">
         <v>45792</v>
       </c>
       <c r="C19" s="29">
@@ -7735,7 +7148,7 @@
     </row>
     <row r="20" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A20" s="26"/>
-      <c r="B20" s="80"/>
+      <c r="B20" s="79"/>
       <c r="C20" s="29"/>
       <c r="D20" s="33"/>
       <c r="E20" s="32">
@@ -7760,7 +7173,7 @@
     </row>
     <row r="21" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A21" s="26"/>
-      <c r="B21" s="80"/>
+      <c r="B21" s="79"/>
       <c r="C21" s="29"/>
       <c r="D21" s="33"/>
       <c r="E21" s="32"/>
@@ -7785,7 +7198,7 @@
     </row>
     <row r="22" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A22" s="26"/>
-      <c r="B22" s="80"/>
+      <c r="B22" s="79"/>
       <c r="C22" s="29"/>
       <c r="D22" s="33"/>
       <c r="E22" s="32"/>
@@ -7809,7 +7222,7 @@
     </row>
     <row r="23" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A23" s="26"/>
-      <c r="B23" s="80"/>
+      <c r="B23" s="79"/>
       <c r="C23" s="29"/>
       <c r="D23" s="33"/>
       <c r="E23" s="32"/>
@@ -7834,7 +7247,7 @@
     </row>
     <row r="24" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A24" s="26"/>
-      <c r="B24" s="80"/>
+      <c r="B24" s="79"/>
       <c r="C24" s="29"/>
       <c r="D24" s="33"/>
       <c r="E24" s="32"/>
@@ -7858,7 +7271,7 @@
     </row>
     <row r="25" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A25" s="26"/>
-      <c r="B25" s="80"/>
+      <c r="B25" s="79"/>
       <c r="C25" s="29"/>
       <c r="D25" s="33"/>
       <c r="E25" s="32"/>
@@ -7882,7 +7295,7 @@
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A26" s="26"/>
-      <c r="B26" s="80"/>
+      <c r="B26" s="79"/>
       <c r="C26" s="29"/>
       <c r="D26" s="33"/>
       <c r="E26" s="32"/>
@@ -7907,7 +7320,7 @@
     </row>
     <row r="27" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A27" s="5"/>
-      <c r="B27" s="81"/>
+      <c r="B27" s="80"/>
       <c r="C27" s="8"/>
       <c r="D27" s="9"/>
       <c r="E27" s="7"/>
@@ -7932,7 +7345,7 @@
     </row>
     <row r="28" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A28" s="5"/>
-      <c r="B28" s="81"/>
+      <c r="B28" s="80"/>
       <c r="C28" s="8"/>
       <c r="D28" s="9"/>
       <c r="E28" s="7"/>
@@ -7956,7 +7369,7 @@
     </row>
     <row r="29" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A29" s="6"/>
-      <c r="B29" s="81"/>
+      <c r="B29" s="80"/>
       <c r="C29" s="8"/>
       <c r="D29" s="10"/>
       <c r="E29" s="14"/>
@@ -8011,7 +7424,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F07CE69-5C67-4DF2-B5BE-CD5590D6A395}">
   <dimension ref="A1:N22"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -8521,7 +7934,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{779217B5-9CE8-46BD-8B22-71F5AA3AD105}">
   <dimension ref="A1:L20"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -8560,7 +7973,7 @@
       <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="73" t="s">
+      <c r="F1" s="72" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="24" t="s">
@@ -8873,7 +8286,7 @@
         <f>H9+H11</f>
         <v>34655.910000000003</v>
       </c>
-      <c r="J12" s="66"/>
+      <c r="J12" s="65"/>
     </row>
     <row r="13" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="26"/>
@@ -8889,7 +8302,7 @@
         <v>-157239.27474799997</v>
       </c>
       <c r="I13" s="15"/>
-      <c r="J13" s="66"/>
+      <c r="J13" s="65"/>
       <c r="L13" s="6"/>
     </row>
     <row r="14" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -8899,7 +8312,7 @@
       <c r="D14" s="33"/>
       <c r="E14" s="32"/>
       <c r="F14" s="37"/>
-      <c r="G14" s="66" t="s">
+      <c r="G14" s="65" t="s">
         <v>30</v>
       </c>
       <c r="H14" s="41">
@@ -8907,8 +8320,8 @@
         <v>-122583.36474799996</v>
       </c>
       <c r="I14" s="15"/>
-      <c r="J14" s="66"/>
-      <c r="L14" s="75"/>
+      <c r="J14" s="65"/>
+      <c r="L14" s="74"/>
     </row>
     <row r="15" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="26"/>
@@ -8924,8 +8337,8 @@
         <v>102430</v>
       </c>
       <c r="I15" s="15"/>
-      <c r="J15" s="66"/>
-      <c r="L15" s="75"/>
+      <c r="J15" s="65"/>
+      <c r="L15" s="74"/>
     </row>
     <row r="16" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="26"/>
@@ -8941,8 +8354,8 @@
         <v>178960</v>
       </c>
       <c r="I16" s="15"/>
-      <c r="J16" s="66"/>
-      <c r="L16" s="75"/>
+      <c r="J16" s="65"/>
+      <c r="L16" s="74"/>
     </row>
     <row r="17" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="26"/>
@@ -8959,7 +8372,7 @@
         <v>281390</v>
       </c>
       <c r="I17" s="15"/>
-      <c r="J17" s="66"/>
+      <c r="J17" s="65"/>
       <c r="L17" s="6"/>
     </row>
     <row r="18" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -8977,30 +8390,30 @@
         <v>-403973.36474799993</v>
       </c>
       <c r="I18" s="15"/>
-      <c r="J18" s="66"/>
+      <c r="J18" s="65"/>
       <c r="L18" s="6"/>
     </row>
     <row r="19" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B19" s="18"/>
-      <c r="G19" s="66" t="s">
+      <c r="G19" s="65" t="s">
         <v>32</v>
       </c>
       <c r="H19" s="6">
         <v>57000</v>
       </c>
       <c r="I19" s="15"/>
-      <c r="J19" s="66"/>
+      <c r="J19" s="65"/>
       <c r="L19" s="6"/>
     </row>
     <row r="20" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="G20" s="66" t="s">
+      <c r="G20" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="H20" s="74">
+      <c r="H20" s="73">
         <f>H18+H19</f>
         <v>-346973.36474799993</v>
       </c>
-      <c r="J20" s="66"/>
+      <c r="J20" s="65"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
@@ -9008,432 +8421,4 @@
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F818BAB4-5237-4BD8-9A61-131DACEE1BB2}">
-  <dimension ref="A1:N19"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.75" style="12" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="10.25" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.125" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="19.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.25" style="11" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
-    <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="10.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" style="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="5"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="28">
-        <v>45705</v>
-      </c>
-      <c r="C2" s="29">
-        <v>4500</v>
-      </c>
-      <c r="D2" s="62">
-        <v>31</v>
-      </c>
-      <c r="E2" s="62">
-        <v>139808.98000000001</v>
-      </c>
-      <c r="F2" s="30">
-        <v>7.35</v>
-      </c>
-      <c r="G2" s="65">
-        <v>33001.74</v>
-      </c>
-      <c r="H2" s="66">
-        <f>G2-E2</f>
-        <v>-106807.24000000002</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="28">
-        <v>45705</v>
-      </c>
-      <c r="C3" s="29">
-        <v>1500</v>
-      </c>
-      <c r="D3" s="62">
-        <v>12</v>
-      </c>
-      <c r="E3" s="62">
-        <v>18039.87</v>
-      </c>
-      <c r="F3" s="30">
-        <v>7.35</v>
-      </c>
-      <c r="G3" s="65">
-        <v>11000.58</v>
-      </c>
-      <c r="H3" s="66">
-        <f>G3-E3</f>
-        <v>-7039.2899999999991</v>
-      </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="28">
-        <v>45712</v>
-      </c>
-      <c r="C4" s="29">
-        <v>15000</v>
-      </c>
-      <c r="D4" s="63">
-        <v>10.9</v>
-      </c>
-      <c r="E4" s="62">
-        <v>163862.14000000001</v>
-      </c>
-      <c r="F4" s="30">
-        <v>2.94</v>
-      </c>
-      <c r="G4" s="67">
-        <v>44002.32</v>
-      </c>
-      <c r="H4" s="66">
-        <f>G4-E4</f>
-        <v>-119859.82</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A5" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="28">
-        <v>45712</v>
-      </c>
-      <c r="C5" s="29">
-        <v>12000</v>
-      </c>
-      <c r="D5" s="63">
-        <v>10</v>
-      </c>
-      <c r="E5" s="62">
-        <v>120265.79</v>
-      </c>
-      <c r="F5" s="30">
-        <v>2.94</v>
-      </c>
-      <c r="G5" s="67">
-        <v>35201.86</v>
-      </c>
-      <c r="H5" s="66">
-        <f>G5-E5</f>
-        <v>-85063.93</v>
-      </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="28">
-        <v>45712</v>
-      </c>
-      <c r="C6" s="29">
-        <v>9000</v>
-      </c>
-      <c r="D6" s="63">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="E6" s="62">
-        <v>83885.39</v>
-      </c>
-      <c r="F6" s="30">
-        <v>2.94</v>
-      </c>
-      <c r="G6" s="67">
-        <v>26401.4</v>
-      </c>
-      <c r="H6" s="66">
-        <f>G6-E6</f>
-        <v>-57483.99</v>
-      </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="27"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="66">
-        <f>SUM(H2:H6)</f>
-        <v>-376254.27</v>
-      </c>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="26"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="66">
-        <f>H7</f>
-        <v>-376254.27</v>
-      </c>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="L8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="26"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="66" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" s="66">
-        <v>321444.99525200005</v>
-      </c>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="L9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="26"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="66" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" s="68">
-        <f>SUM(H8,H9)</f>
-        <v>-54809.274747999967</v>
-      </c>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="L10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="26"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="66" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="69">
-        <v>43930</v>
-      </c>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="L11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="26"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="66" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" s="69">
-        <v>58500</v>
-      </c>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="L12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="26"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="61" t="s">
-        <v>61</v>
-      </c>
-      <c r="G13" s="66" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="68">
-        <f>H11+H12</f>
-        <v>102430</v>
-      </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="L13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="26"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="66" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="70">
-        <f>H10-H13</f>
-        <v>-157239.27474799997</v>
-      </c>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="L14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="26"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="61" t="s">
-        <v>60</v>
-      </c>
-      <c r="G15" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="H15" s="66">
-        <v>57000</v>
-      </c>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="L15" s="6"/>
-    </row>
-    <row r="16" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="26"/>
-      <c r="B16" s="64"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="66" t="s">
-        <v>33</v>
-      </c>
-      <c r="H16" s="71">
-        <f>H14+H15</f>
-        <v>-100239.27474799997</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="26"/>
-      <c r="B17" s="64"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="66"/>
-      <c r="H17" s="66"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="26"/>
-      <c r="B18" s="64"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="61" t="s">
-        <v>62</v>
-      </c>
-      <c r="G18" s="72" t="s">
-        <v>63</v>
-      </c>
-      <c r="H18" s="66">
-        <f>H15-H13</f>
-        <v>-45430</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
 </file>